--- a/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_matplaceItemDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb85b1299b9076c2/ドキュメント/Unity/Okashi_Atlier2/Assets/Resources/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F321FB8F-F115-48E0-BC83-C009996654ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{F321FB8F-F115-48E0-BC83-C009996654ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33DF2EDC-B971-4D2F-8BD6-E0C291E3B3E5}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25050" windowHeight="13455" activeTab="3" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3165" yWindow="1755" windowWidth="23295" windowHeight="13305" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="01_map_Grt" sheetId="1" r:id="rId1"/>
@@ -1865,6 +1865,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8823,16 +8827,16 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -8898,16 +8902,16 @@
         <v>27</v>
       </c>
       <c r="AA16">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC16">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AD16">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AE16">
         <v>0</v>
@@ -8937,10 +8941,10 @@
         <v>0</v>
       </c>
       <c r="AN16" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AO16" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AP16">
         <v>0</v>
@@ -8952,13 +8956,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="E17" t="s">
         <v>151</v>
@@ -9081,16 +9085,16 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C18" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="D18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E18" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -9156,16 +9160,16 @@
         <v>27</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AB18">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AC18">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AD18">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -9195,10 +9199,10 @@
         <v>0</v>
       </c>
       <c r="AN18" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AO18" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AP18">
         <v>0</v>
@@ -11457,7 +11461,7 @@
         <v>254</v>
       </c>
       <c r="T36" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="U36" t="s">
         <v>129</v>
@@ -11706,7 +11710,7 @@
         <v>230</v>
       </c>
       <c r="Q38" t="s">
-        <v>231</v>
+        <v>27</v>
       </c>
       <c r="R38" t="s">
         <v>217</v>
@@ -11718,7 +11722,7 @@
         <v>33</v>
       </c>
       <c r="U38" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="V38" t="s">
         <v>27</v>
@@ -11736,7 +11740,7 @@
         <v>266</v>
       </c>
       <c r="AA38">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="AB38">
         <v>17</v>
@@ -11745,19 +11749,19 @@
         <v>9</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AF38">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI38">
         <v>0</v>
@@ -14010,13 +14014,13 @@
         <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
         <v>142</v>
@@ -14085,16 +14089,16 @@
         <v>27</v>
       </c>
       <c r="AA16">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC16">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AD16">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AE16">
         <v>0</v>
@@ -14124,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="AN16" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AO16" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="AP16">
         <v>0</v>
@@ -14139,13 +14143,13 @@
         <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
@@ -14268,13 +14272,13 @@
         <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C18" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="D18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E18" t="s">
         <v>142</v>
@@ -14343,16 +14347,16 @@
         <v>27</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AB18">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AC18">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AD18">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -14382,10 +14386,10 @@
         <v>0</v>
       </c>
       <c r="AN18" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="AO18" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="AP18">
         <v>0</v>
@@ -16644,7 +16648,7 @@
         <v>254</v>
       </c>
       <c r="T36" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="U36" t="s">
         <v>129</v>
@@ -16893,7 +16897,7 @@
         <v>230</v>
       </c>
       <c r="Q38" t="s">
-        <v>231</v>
+        <v>27</v>
       </c>
       <c r="R38" t="s">
         <v>217</v>
@@ -16905,7 +16909,7 @@
         <v>33</v>
       </c>
       <c r="U38" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="V38" t="s">
         <v>27</v>
@@ -16923,7 +16927,7 @@
         <v>266</v>
       </c>
       <c r="AA38">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="AB38">
         <v>17</v>
@@ -16932,19 +16936,19 @@
         <v>9</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AF38">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI38">
         <v>0</v>
